--- a/data/trans_orig/P19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2007</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237610</t>
+          <t>240275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>266677</t>
+          <t>269068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>327885</t>
+          <t>330320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>467697</t>
+          <t>468638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>547050</t>
+          <t>547928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>794113</t>
+          <t>791448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>843886</t>
+          <t>844918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>986303</t>
+          <t>983868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1047511</t>
+          <t>1045120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1798861</t>
+          <t>1797983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1878214</t>
+          <t>1877273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>397679</t>
+          <t>399471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>472232</t>
+          <t>469335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>550821</t>
+          <t>548774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>625805</t>
+          <t>626406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>969822</t>
+          <t>966852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1076646</t>
+          <t>1074334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1220269</t>
+          <t>1223166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1294822</t>
+          <t>1293030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961868</t>
+          <t>961267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1036852</t>
+          <t>1038899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2203528</t>
+          <t>2205840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2310352</t>
+          <t>2313322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147119</t>
+          <t>148165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191522</t>
+          <t>193606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154156</t>
+          <t>152771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196898</t>
+          <t>195514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314075</t>
+          <t>316274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371742</t>
+          <t>378079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359886</t>
+          <t>357802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>404289</t>
+          <t>403243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279514</t>
+          <t>280898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322256</t>
+          <t>323641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656078</t>
+          <t>649741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>713745</t>
+          <t>711546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>765770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>862782</t>
+          <t>869320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1006886</t>
+          <t>1006060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1110122</t>
+          <t>1115428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1798612</t>
+          <t>1794572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1942870</t>
+          <t>1949930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2412849</t>
+          <t>2406311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2514495</t>
+          <t>2509861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2268150</t>
+          <t>2262844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2371386</t>
+          <t>2372212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4711034</t>
+          <t>4703974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4855292</t>
+          <t>4859332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2012</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137318</t>
+          <t>139393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182697</t>
+          <t>183727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278243</t>
+          <t>277030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340932</t>
+          <t>344595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>427606</t>
+          <t>425373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>510171</t>
+          <t>505707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>790796</t>
+          <t>789766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>836175</t>
+          <t>834100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>996865</t>
+          <t>993202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1059554</t>
+          <t>1060767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1801119</t>
+          <t>1805583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1883684</t>
+          <t>1885917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>465236</t>
+          <t>469050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>547491</t>
+          <t>547497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>541303</t>
+          <t>540616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>621735</t>
+          <t>618959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1029157</t>
+          <t>1035408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1145426</t>
+          <t>1143140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1415103</t>
+          <t>1415097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1497358</t>
+          <t>1493544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1135103</t>
+          <t>1137879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1215535</t>
+          <t>1216222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2574006</t>
+          <t>2576292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2690275</t>
+          <t>2684024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153319</t>
+          <t>154535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200028</t>
+          <t>200099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168232</t>
+          <t>166761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211322</t>
+          <t>210760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>334289</t>
+          <t>335116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>396027</t>
+          <t>400048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281153</t>
+          <t>281082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327862</t>
+          <t>326646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247309</t>
+          <t>247871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290399</t>
+          <t>291870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543786</t>
+          <t>539765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605524</t>
+          <t>604697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>796561</t>
+          <t>794692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>898719</t>
+          <t>898793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1020365</t>
+          <t>1019868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1132509</t>
+          <t>1132346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1840078</t>
+          <t>1842901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1998667</t>
+          <t>1995710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2518550</t>
+          <t>2518476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2620708</t>
+          <t>2622577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2420757</t>
+          <t>2420920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2532901</t>
+          <t>2533398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4971868</t>
+          <t>4974825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5130457</t>
+          <t>5127634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2016</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109241</t>
+          <t>109956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151388</t>
+          <t>150985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204251</t>
+          <t>203811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>258891</t>
+          <t>261250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328706</t>
+          <t>326502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398065</t>
+          <t>394028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602959</t>
+          <t>603362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>645106</t>
+          <t>644391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>735769</t>
+          <t>733410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>790409</t>
+          <t>790849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1350942</t>
+          <t>1354979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1420301</t>
+          <t>1422505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>602397</t>
+          <t>601758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>689404</t>
+          <t>685994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>711407</t>
+          <t>714557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>796993</t>
+          <t>799008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1342703</t>
+          <t>1343185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1466439</t>
+          <t>1466668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1386981</t>
+          <t>1390391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1473988</t>
+          <t>1474627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1191307</t>
+          <t>1189292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1276893</t>
+          <t>1273743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2598246</t>
+          <t>2598017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2721982</t>
+          <t>2721500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186842</t>
+          <t>188699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233456</t>
+          <t>235017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204728</t>
+          <t>203172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252581</t>
+          <t>253520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>404396</t>
+          <t>403763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>471040</t>
+          <t>473740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313430</t>
+          <t>311869</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>360044</t>
+          <t>358187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296559</t>
+          <t>295620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344412</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624987</t>
+          <t>622287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>691631</t>
+          <t>692264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>929340</t>
+          <t>931128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1041855</t>
+          <t>1039144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,82 +4983,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1216765</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1157361</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1272151</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2202156</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2131888</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2290692</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>31,87%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>30,85%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1216765</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1159518</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1274180</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2202156</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2123149</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2276326</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2335763</t>
+          <t>2338474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2448278</t>
+          <t>2446490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,82 +5096,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2315335</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2259949</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2374739</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>65,55%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>63,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>67,23%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4707562</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>4619026</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4777830</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>68,13%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>69,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2315335</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2257920</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2372582</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>67,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4462</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>4707562</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>4633392</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4786569</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>67,06%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2023</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2023 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74187</t>
+          <t>75046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105779</t>
+          <t>108996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110285</t>
+          <t>111922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140785</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>193748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238633</t>
+          <t>236531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404088</t>
+          <t>400871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435680</t>
+          <t>434821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>601230</t>
+          <t>599010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631730</t>
+          <t>630093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1013248</t>
+          <t>1015350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1059010</t>
+          <t>1058133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368566</t>
+          <t>364275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>629674</t>
+          <t>625048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>467051</t>
+          <t>474487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>748433</t>
+          <t>758915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>981925</t>
+          <t>947525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1357624</t>
+          <t>1340773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1646168</t>
+          <t>1650794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1907276</t>
+          <t>1911567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1473143</t>
+          <t>1462661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1754525</t>
+          <t>1747089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3139794</t>
+          <t>3156645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3515493</t>
+          <t>3549893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203485</t>
+          <t>202844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>255122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279614</t>
+          <t>279876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>323296</t>
+          <t>324927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496057</t>
+          <t>496856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>563863</t>
+          <t>566080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387879</t>
+          <t>387937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>439574</t>
+          <t>440215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334565</t>
+          <t>332934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378247</t>
+          <t>377985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>737057</t>
+          <t>734840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804863</t>
+          <t>804064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>659363</t>
+          <t>673374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>945211</t>
+          <t>948901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>864974</t>
+          <t>880319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1179787</t>
+          <t>1185502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +6621,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1942535</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1683697</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2090970</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>23,88%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2402</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1942535</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1714818</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2102443</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2483557</t>
+          <t>2479867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2769405</t>
+          <t>2755394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2441664</t>
+          <t>2435949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2756477</t>
+          <t>2741132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,47 +6734,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>75,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6240</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>5107684</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>4959249</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5366522</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>76,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6240</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>5107684</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>4947776</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5335401</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>72,45%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>70,18%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>186805</t>
+          <t>187264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240275</t>
+          <t>236608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>269068</t>
+          <t>265949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330320</t>
+          <t>328632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>468638</t>
+          <t>467604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>547928</t>
+          <t>545684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>791448</t>
+          <t>795115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>844918</t>
+          <t>844459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>983868</t>
+          <t>985556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1045120</t>
+          <t>1048239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1797983</t>
+          <t>1800227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1877273</t>
+          <t>1878307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399471</t>
+          <t>393226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>469335</t>
+          <t>469441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>548774</t>
+          <t>547084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>626406</t>
+          <t>624295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>966852</t>
+          <t>970193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1074334</t>
+          <t>1078895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1223166</t>
+          <t>1223060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1293030</t>
+          <t>1299275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961267</t>
+          <t>963378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1038899</t>
+          <t>1040589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2205840</t>
+          <t>2201279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2313322</t>
+          <t>2309981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148165</t>
+          <t>149193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193606</t>
+          <t>192132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152771</t>
+          <t>153293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195514</t>
+          <t>197053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>316274</t>
+          <t>313467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378079</t>
+          <t>378739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>357802</t>
+          <t>359276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>403243</t>
+          <t>402215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280898</t>
+          <t>279359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323641</t>
+          <t>323119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649741</t>
+          <t>649081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>711546</t>
+          <t>714353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>767116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>869320</t>
+          <t>869016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1006060</t>
+          <t>1007614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1115428</t>
+          <t>1115681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1794572</t>
+          <t>1806499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1949930</t>
+          <t>1946168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2406311</t>
+          <t>2406615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2509861</t>
+          <t>2508515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2262844</t>
+          <t>2262591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2372212</t>
+          <t>2370658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4703974</t>
+          <t>4707736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4859332</t>
+          <t>4847405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139393</t>
+          <t>138281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>185021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277030</t>
+          <t>279043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>344595</t>
+          <t>341931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>425373</t>
+          <t>430562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>505707</t>
+          <t>511356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>789766</t>
+          <t>788472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>834100</t>
+          <t>835212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>993202</t>
+          <t>995866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1060767</t>
+          <t>1058754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1805583</t>
+          <t>1799934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1885917</t>
+          <t>1880728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>469050</t>
+          <t>469942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>547497</t>
+          <t>551419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>540616</t>
+          <t>541762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>618959</t>
+          <t>623116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1035408</t>
+          <t>1032802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1143140</t>
+          <t>1146324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1415097</t>
+          <t>1411175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1493544</t>
+          <t>1492652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1137879</t>
+          <t>1133722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1216222</t>
+          <t>1215076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2576292</t>
+          <t>2573108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2684024</t>
+          <t>2686630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154535</t>
+          <t>153495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200099</t>
+          <t>198973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166761</t>
+          <t>167184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210760</t>
+          <t>211103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>335116</t>
+          <t>332976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400048</t>
+          <t>401560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281082</t>
+          <t>282208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>326646</t>
+          <t>327686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247871</t>
+          <t>247528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291870</t>
+          <t>291447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>539765</t>
+          <t>538253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604697</t>
+          <t>606837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>794692</t>
+          <t>789795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>898793</t>
+          <t>899048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1019868</t>
+          <t>1025573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1132346</t>
+          <t>1140899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1842901</t>
+          <t>1844378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1995710</t>
+          <t>1996037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2518476</t>
+          <t>2518221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2622577</t>
+          <t>2627474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2420920</t>
+          <t>2412367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2533398</t>
+          <t>2527693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4974825</t>
+          <t>4974498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5127634</t>
+          <t>5126157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109956</t>
+          <t>108663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150985</t>
+          <t>150829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203811</t>
+          <t>204505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>261250</t>
+          <t>260906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>326502</t>
+          <t>328902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>394028</t>
+          <t>397835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>603362</t>
+          <t>603518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>644391</t>
+          <t>645684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>733410</t>
+          <t>733754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>790849</t>
+          <t>790155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1354979</t>
+          <t>1351172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1422505</t>
+          <t>1420105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>601758</t>
+          <t>600807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>685994</t>
+          <t>690367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>714557</t>
+          <t>716014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>799008</t>
+          <t>805275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1343185</t>
+          <t>1342728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1466668</t>
+          <t>1466858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1390391</t>
+          <t>1386018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1474627</t>
+          <t>1475578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1189292</t>
+          <t>1183025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1273743</t>
+          <t>1272286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2598017</t>
+          <t>2597827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2721500</t>
+          <t>2721957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188699</t>
+          <t>186275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235017</t>
+          <t>234224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203172</t>
+          <t>206349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253520</t>
+          <t>250336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>403763</t>
+          <t>406666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>473740</t>
+          <t>472323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311869</t>
+          <t>312662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>358187</t>
+          <t>360611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295620</t>
+          <t>298804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345968</t>
+          <t>342791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622287</t>
+          <t>623704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692264</t>
+          <t>689361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>931128</t>
+          <t>937022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1039144</t>
+          <t>1039480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1157361</t>
+          <t>1162246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1272151</t>
+          <t>1279956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2131888</t>
+          <t>2123961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2290692</t>
+          <t>2288370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2338474</t>
+          <t>2338138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2446490</t>
+          <t>2440596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2259949</t>
+          <t>2252144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2374739</t>
+          <t>2369854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4619026</t>
+          <t>4621348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4777830</t>
+          <t>4785757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89463</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75046</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108996</t>
+          <t>112861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125337</t>
+          <t>136045</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111922</t>
+          <t>121334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143005</t>
+          <t>155534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>214800</t>
+          <t>231619</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193748</t>
+          <t>208584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236531</t>
+          <t>256608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>420404</t>
+          <t>477270</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400871</t>
+          <t>459984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434821</t>
+          <t>494151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>616678</t>
+          <t>673211</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>599010</t>
+          <t>653722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630093</t>
+          <t>687922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1037081</t>
+          <t>1150483</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1015350</t>
+          <t>1125494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1058133</t>
+          <t>1173518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>509867</t>
+          <t>572845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>509867</t>
+          <t>572845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>509867</t>
+          <t>572845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>742015</t>
+          <t>809256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>742015</t>
+          <t>809256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>742015</t>
+          <t>809256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1251881</t>
+          <t>1382102</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1251881</t>
+          <t>1382102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1251881</t>
+          <t>1382102</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>570873</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364275</t>
+          <t>520755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>625048</t>
+          <t>618033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>655344</t>
+          <t>684814</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>474487</t>
+          <t>645417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>758915</t>
+          <t>725490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1197135</t>
+          <t>1255687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>947525</t>
+          <t>1193106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1340773</t>
+          <t>1319807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1734051</t>
+          <t>1644613</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1650794</t>
+          <t>1597453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1911567</t>
+          <t>1694731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1566232</t>
+          <t>1467280</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1462661</t>
+          <t>1426604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1747089</t>
+          <t>1506677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3300283</t>
+          <t>3111894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3156645</t>
+          <t>3047774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3549893</t>
+          <t>3174475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2275842</t>
+          <t>2215486</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2275842</t>
+          <t>2215486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2275842</t>
+          <t>2215486</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2221576</t>
+          <t>2152094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2221576</t>
+          <t>2152094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2221576</t>
+          <t>2152094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4497418</t>
+          <t>4367581</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4497418</t>
+          <t>4367581</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4497418</t>
+          <t>4367581</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>229029</t>
+          <t>253239</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202844</t>
+          <t>227311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255122</t>
+          <t>281491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>301571</t>
+          <t>329009</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279876</t>
+          <t>304052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>324927</t>
+          <t>352951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>530601</t>
+          <t>582248</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496856</t>
+          <t>545840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566080</t>
+          <t>618377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414030</t>
+          <t>454323</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>426071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440215</t>
+          <t>480251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>356290</t>
+          <t>401764</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332934</t>
+          <t>377822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>377985</t>
+          <t>426721</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>770319</t>
+          <t>856087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>734840</t>
+          <t>819958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>804064</t>
+          <t>892495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>643059</t>
+          <t>707562</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>643059</t>
+          <t>707562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643059</t>
+          <t>707562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657861</t>
+          <t>730773</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657861</t>
+          <t>730773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657861</t>
+          <t>730773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1300920</t>
+          <t>1438335</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1300920</t>
+          <t>1438335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1300920</t>
+          <t>1438335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>860283</t>
+          <t>919686</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>673374</t>
+          <t>856468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>948901</t>
+          <t>978959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,67 +6601,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1082252</t>
+          <t>1149869</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>880319</t>
+          <t>1101906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1185502</t>
+          <t>1204694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>31,14%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>32,63%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2069555</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1989692</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2147520</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>28,79%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>29,88%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>24,31%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2402</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1942535</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1683697</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2090970</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2568485</t>
+          <t>2576207</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2479867</t>
+          <t>2516934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2755394</t>
+          <t>2639425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,67 +6714,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2539199</t>
+          <t>2542255</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2435949</t>
+          <t>2487430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2741132</t>
+          <t>2590218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>68,86%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>67,37%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>70,16%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6240</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>5118462</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>5040497</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5198325</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>71,21%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>70,12%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>67,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>75,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6240</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>5107684</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>4959249</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5366522</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>72,45%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>70,34%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3428768</t>
+          <t>3495893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3428768</t>
+          <t>3495893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3428768</t>
+          <t>3495893</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3621451</t>
+          <t>3692124</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3621451</t>
+          <t>3692124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3621451</t>
+          <t>3692124</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7050219</t>
+          <t>7188017</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7050219</t>
+          <t>7188017</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7050219</t>
+          <t>7188017</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
